--- a/VerveStacks_NGA_grids_kan10/SuppXLS/Scen_TSParameters_ts_annual.xlsx
+++ b/VerveStacks_NGA_grids_kan10/SuppXLS/Scen_TSParameters_ts_annual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BF24964-9DB6-402A-949F-C6F0D6DC95A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35D7A754-C207-49BB-901D-12FF5ADEFA2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1386,7 +1386,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88017155-246D-430F-81C8-4E07FE67EC93}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F13574D-ACF3-429B-BC75-E8DB7A4233DF}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1443,7 +1443,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B865B446-EDBA-435C-9ED6-DA604B7A4C38}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39F7C9E5-9B12-42A4-BBF8-AE431B78703B}">
   <dimension ref="B9:O46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2453,7 +2453,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9D2C0DB-7770-42D0-AC9D-D79912FDECBC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB6D51A-534D-4BC2-8C47-FCAB83A0F01B}">
   <dimension ref="B9:T83"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4703,7 +4703,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C86DCF7B-6EF3-4CE7-BD69-46B7918A49CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{419E3D64-734F-4CF2-85B1-8D1C550AF4AD}">
   <dimension ref="B9:E11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4747,7 +4747,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F97F560C-F3DA-43E5-AA12-E515FEE49FB4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59359633-78BE-45B2-AD48-4785C01FA21F}">
   <dimension ref="B9:D12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4796,7 +4796,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173AC6ED-4177-484A-AE5E-4E9142D5A761}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{181014F3-45E5-4126-8827-A900043A3BBC}">
   <dimension ref="B9:D11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4834,7 +4834,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24C4545B-A984-4019-82C9-4D6DF528FE01}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE93FD3A-EE72-47CB-9585-2650FB33C35A}">
   <dimension ref="B9:E39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4880,7 +4880,7 @@
         <v>37</v>
       </c>
       <c r="D12">
-        <v>0.3812166666666667</v>
+        <v>0.38121666666666659</v>
       </c>
       <c r="E12" t="s">
         <v>213</v>
@@ -4894,7 +4894,7 @@
         <v>37</v>
       </c>
       <c r="D13">
-        <v>0.42086666666666667</v>
+        <v>0.42086666666666672</v>
       </c>
       <c r="E13" t="s">
         <v>213</v>
@@ -4922,7 +4922,7 @@
         <v>37</v>
       </c>
       <c r="D15">
-        <v>0.41880833333333328</v>
+        <v>0.41880833333333339</v>
       </c>
       <c r="E15" t="s">
         <v>213</v>
@@ -4950,7 +4950,7 @@
         <v>37</v>
       </c>
       <c r="D17">
-        <v>0.39129999999999998</v>
+        <v>0.39130000000000004</v>
       </c>
       <c r="E17" t="s">
         <v>213</v>
@@ -4978,7 +4978,7 @@
         <v>37</v>
       </c>
       <c r="D19">
-        <v>0.33904166666666669</v>
+        <v>0.33904166666666663</v>
       </c>
       <c r="E19" t="s">
         <v>213</v>
@@ -5006,7 +5006,7 @@
         <v>37</v>
       </c>
       <c r="D21">
-        <v>0.27826666666666666</v>
+        <v>0.27826666666666661</v>
       </c>
       <c r="E21" t="s">
         <v>213</v>
@@ -5020,7 +5020,7 @@
         <v>37</v>
       </c>
       <c r="D22">
-        <v>0.32745000000000002</v>
+        <v>0.32745000000000007</v>
       </c>
       <c r="E22" t="s">
         <v>213</v>
@@ -5076,7 +5076,7 @@
         <v>37</v>
       </c>
       <c r="D26">
-        <v>0.32669999999999999</v>
+        <v>0.32670000000000005</v>
       </c>
       <c r="E26" t="s">
         <v>213</v>
@@ -5090,7 +5090,7 @@
         <v>37</v>
       </c>
       <c r="D27">
-        <v>0.39637499999999998</v>
+        <v>0.39637499999999992</v>
       </c>
       <c r="E27" t="s">
         <v>213</v>
@@ -5132,7 +5132,7 @@
         <v>37</v>
       </c>
       <c r="D30">
-        <v>0.34900000000000003</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="E30" t="s">
         <v>213</v>
@@ -5160,7 +5160,7 @@
         <v>37</v>
       </c>
       <c r="D32">
-        <v>0.37109999999999999</v>
+        <v>0.37110000000000004</v>
       </c>
       <c r="E32" t="s">
         <v>213</v>
@@ -5174,7 +5174,7 @@
         <v>37</v>
       </c>
       <c r="D33">
-        <v>0.42145000000000005</v>
+        <v>0.42144999999999994</v>
       </c>
       <c r="E33" t="s">
         <v>213</v>
@@ -5188,7 +5188,7 @@
         <v>37</v>
       </c>
       <c r="D34">
-        <v>0.39028333333333326</v>
+        <v>0.39028333333333332</v>
       </c>
       <c r="E34" t="s">
         <v>213</v>
@@ -5202,7 +5202,7 @@
         <v>37</v>
       </c>
       <c r="D35">
-        <v>0.35414166666666674</v>
+        <v>0.35414166666666663</v>
       </c>
       <c r="E35" t="s">
         <v>213</v>
@@ -5216,7 +5216,7 @@
         <v>37</v>
       </c>
       <c r="D36">
-        <v>0.41026666666666661</v>
+        <v>0.41026666666666672</v>
       </c>
       <c r="E36" t="s">
         <v>213</v>
